--- a/data/trans_dic/P79A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P79A_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,29</t>
+          <t>0,13; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,17</t>
+          <t>0,21; 2,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,25</t>
+          <t>0,31; 1,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,45</t>
+          <t>0,6; 2,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,52</t>
+          <t>0,41; 1,72</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,94</t>
+          <t>1,35; 4,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,51</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,29</t>
+          <t>1,18; 3,43</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,37</t>
+          <t>2,29; 5,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,2</t>
+          <t>0,95; 2,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,62</t>
+          <t>1,85; 3,6</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,3</t>
+          <t>3,09; 7,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,37</t>
+          <t>2,39; 5,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,62</t>
+          <t>3,03; 5,41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,54</t>
+          <t>1,91; 4,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,48</t>
+          <t>1,51; 3,71</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,69</t>
+          <t>1,84; 3,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,6</t>
+          <t>1,75; 2,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,44</t>
+          <t>1,89; 2,73</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>7173</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>166; 6536</t>
+          <t>732; 8411</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>325; 9729</t>
+          <t>1045; 11604</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1816; 11879</t>
+          <t>3181; 14882</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>8095</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9142</t>
+          <t>0; 8118</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1765; 9362</t>
+          <t>2523; 10527</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3054; 12682</t>
+          <t>3699; 15584</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>14092</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2014; 19620</t>
+          <t>6370; 21580</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163; 4189</t>
+          <t>0; 5520</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3414; 19092</t>
+          <t>7791; 22626</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>36439</t>
+          <t>37956</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48880</t>
+          <t>51374</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23537; 55614</t>
+          <t>25921; 60432</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5863; 21533</t>
+          <t>8151; 21404</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31208; 72936</t>
+          <t>36970; 71655</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24110</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43412</t>
+          <t>56148</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11244; 29909</t>
+          <t>17545; 43289</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15768; 36801</t>
+          <t>19896; 41994</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30834; 60752</t>
+          <t>42428; 75695</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24725</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24725</t>
+          <t>25595</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15816; 42160</t>
+          <t>16115; 39173</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14168; 44835</t>
+          <t>16322; 40093</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>69186</t>
+          <t>82813</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>69596</t>
+          <t>79664</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>138782</t>
+          <t>162477</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>48910; 90840</t>
+          <t>63375; 110807</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>52648; 93040</t>
+          <t>63656; 100402</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>110708; 169428</t>
+          <t>133890; 192977</t>
         </is>
       </c>
     </row>
